--- a/tests/test_25_10.xlsx
+++ b/tests/test_25_10.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\tools\git_repo\LEnsE\ressources\lensecam\tests\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\_tools\git_repo\LEnsE\ressources\lensecam\tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE2DEDBF-CF6B-4FED-9EDB-532AB5C1BAFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EF44134-BA89-486A-9080-5F0D1ED92750}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Obscurité" sheetId="2" r:id="rId1"/>
@@ -2371,7 +2371,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="fr-FR"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -7531,10 +7531,10 @@
       <xdr:rowOff>23811</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>219074</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>9524</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>571500</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
